--- a/input/14_programs.xlsx
+++ b/input/14_programs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_0697CBB35DAAB011286609F9836032973CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03829D50-CEDF-4B0A-B9D7-4E08E63BE45B}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_0697CBB35DAAB011286609F9836032973CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26C4367B-79C3-4914-A3D9-2400C000294F}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="32">
   <si>
     <t>Program</t>
   </si>
@@ -146,7 +146,19 @@
     <t>Last Row</t>
   </si>
   <si>
-    <t>utility_fuel</t>
+    <t>Utility</t>
+  </si>
+  <si>
+    <t>fuel</t>
+  </si>
+  <si>
+    <t>test_utility_1</t>
+  </si>
+  <si>
+    <t>test_utility_2</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -156,7 +168,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,8 +200,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0B1D2F"/>
+      <name val="Helvetica-Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0B1D2F"/>
+      <name val="Helvetica-Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +232,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -257,7 +295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -299,10 +337,17 @@
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -640,417 +685,1522 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="43.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="15" t="s">
+      <c r="C1" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="15" t="s">
+      <c r="B2" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="15" t="s">
+      <c r="B3" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="15" t="s">
+      <c r="B4" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="B5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="B7" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="15" t="s">
+      <c r="B8" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="15" t="s">
+      <c r="B9" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="15" t="s">
+      <c r="B10" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="15" t="s">
+      <c r="B11" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="15" t="s">
+      <c r="B12" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="15" t="s">
+      <c r="B13" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="15" t="s">
+      <c r="B14" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="15" t="s">
+      <c r="B15" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="15" t="s">
+      <c r="B16" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="15" t="s">
+      <c r="B17" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="15" t="s">
+      <c r="B18" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="15" t="s">
+      <c r="B19" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="15" t="s">
+      <c r="B20" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="15" t="s">
+      <c r="B21" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="15" t="s">
+      <c r="B22" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="15" t="s">
+      <c r="B23" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="15" t="s">
+      <c r="B24" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="15" t="s">
+      <c r="B25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="15" t="s">
+      <c r="B26" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="15" t="s">
+      <c r="B27" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="15" t="s">
+      <c r="B28" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="15" t="s">
+      <c r="B29" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="15" t="s">
+      <c r="B30" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="15" t="s">
+      <c r="B31" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="15" t="s">
+      <c r="B32" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="15" t="s">
+      <c r="B33" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="15" t="s">
+      <c r="B34" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="15" t="s">
+      <c r="B35" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="15" t="s">
+      <c r="B36" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37">
+      <c r="B37" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B104" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B106" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="21">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="21">
         <v>0.3</v>
       </c>
     </row>
